--- a/outputs/Fish_passage_injury_mortality_extraction.xlsx
+++ b/outputs/Fish_passage_injury_mortality_extraction.xlsx
@@ -430,14 +430,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T229"/>
+  <dimension ref="A1:T256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -451,7 +451,7 @@
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="51" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr"/>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr"/>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr"/>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr"/>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr"/>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr"/>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr"/>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr"/>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr"/>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr"/>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr"/>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S113" s="2" t="inlineStr"/>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr"/>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S152" s="2" t="inlineStr"/>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="R154" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S154" s="2" t="inlineStr"/>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="R159" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S159" s="2" t="inlineStr"/>
@@ -13245,7 +13245,7 @@
       </c>
       <c r="R168" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S168" s="2" t="inlineStr"/>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="R187" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S187" s="2" t="inlineStr"/>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="R209" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Mined</t>
         </is>
       </c>
       <c r="S209" s="2" t="inlineStr"/>
@@ -17573,6 +17573,2016 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>1980_Weitkamp</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Weitkamp</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>10.1577/1548-8659(1980)109&lt;659:ARODGS&gt;2.0.CO;2</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>A review of dissolved gas supersaturation literature</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Gas supersaturation/GBT</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Rainbow trout/steelhead (O. mykiss); Sockeye/coho (Oncorhynchus); Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>12-15 cm; 16.5-19.5 cm</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>117% survivo; 110% mortali; 5% mortali; 50% mortali; 124% mortali; 80% mortali; 10% mortali; 115% mortali; 27% mortali; 118% mortali</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>Review/meta-analysis</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr"/>
+      <c r="Q230" s="2" t="inlineStr"/>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>1997_Coutant</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Coutant</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Development of biological criteria for the design of advanced hydropower turbines</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Shear; Cavitation; Turbulence; Grinding/abrasion/pinch</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>Salmonids (general); Smolts (unspec.); Sockeye/coho (Oncorhynchus); Chinook salmon (O. tshawytscha)</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>Egg; Larva</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>pressure kPa: 0.035, 0.040, 0.2, 0.5, 1.6, 1.9</t>
+        </is>
+      </c>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>4% mortali; 5.2% mortali; 1.7% mortali</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr"/>
+      <c r="O231" s="2" t="inlineStr"/>
+      <c r="P231" s="2" t="inlineStr"/>
+      <c r="Q231" s="2" t="inlineStr"/>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2000_Mathur</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Mathur</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/j.1752-1688.2000.tb04302.x</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Salmonid smolt survival relative to turbine efficiency and entrainment depth in hydroelectric power generation</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Shear; Cavitation; Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Salmonids (general); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Smolt; Yearling/sub-adult</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>Kaplan</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr"/>
+      <c r="P232" s="2" t="inlineStr"/>
+      <c r="Q232" s="2" t="inlineStr"/>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2000_Turnpenny</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Turnpenny</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Risk assessment for fish passage through small, low-head turbines</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>Salmonids (general); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Smolt</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>2% injurie; 35.4% mortali</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>56; 24; 9; 132; 65</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>Tidal</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>CFD/numerical</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr"/>
+      <c r="Q233" s="2" t="inlineStr"/>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2001_Killgore</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Killgore</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>10.1577/1548-8675(2001)021&lt;0947:EOPIMO&gt;2.0.CO;2</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation of propeller-induced mortality on early life stages of selected fish species</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Shear</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>Common carp (C. carpio); White sturgeon (A. transmontanus)</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Egg; Larva; Juvenile; Adult</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>10% mortali; 45% mortali; 17% mortali; 75% mortali; 40% mortali; 100% mortali</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>Propeller/axial</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>Shear flume/jet</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr"/>
+      <c r="Q234" s="2" t="inlineStr"/>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2002_Humphries</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Humphries</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>10.1046/j.1365-2427.2002.00871.x</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>River regulation and fish larvae: variation through space and time</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>Gudgeon (Gobio gobio); Murray cod (M. peelii); Common carp (C. carpio); Golden perch (M. ambigua)</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Egg; Larva; Juvenile; Adult</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr"/>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="2" t="inlineStr"/>
+      <c r="O235" s="2" t="inlineStr"/>
+      <c r="P235" s="2" t="inlineStr"/>
+      <c r="Q235" s="2" t="inlineStr"/>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2008_Larinier</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Larinier</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10750-008-9398-9</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Fish passage experience at small-scale hydro-electric power plants in France</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>15-30 cm</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>strain rate s-1: 1007</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>5% mortali; 95% surviva</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>Weir</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr"/>
+      <c r="P236" s="2" t="inlineStr"/>
+      <c r="Q236" s="2" t="inlineStr"/>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2010_Calles</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Calles</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/j.1365-2427.2010.02459.x</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Size-dependent mortality of migratory silver eels at a hydropower plant, and implications for escapement to the sea</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>European eel (A. anguilla)</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Larva; Juvenile; Adult</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>737-12 mm; 590-930 mm; 500-680 mm; 525-930 mm; 500-850 mm; 726-21 mm</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>60% mortali; 100% mortali</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>50; 15; 6; 5; 8; 4; 46; 16</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="inlineStr"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>Telemetry/tagging</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr"/>
+      <c r="Q237" s="2" t="inlineStr"/>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2012_Baumgartner</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Baumgartner</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/j.1442-8903.2012.00655.x</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Reducing the perversion of diversion: applying world-standard fish screening practices to the Murray-Darling Basin</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Salmonids (general); Bull trout (S. confluentus); Murray cod (M. peelii); Golden perch (M. ambigua)</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr"/>
+      <c r="O238" s="2" t="inlineStr"/>
+      <c r="P238" s="2" t="inlineStr"/>
+      <c r="Q238" s="2" t="inlineStr"/>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2013_Bracken</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Bracken</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>10.1002/rra.2596</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Potential impacts of small-scale hydroelectric power generation on downstream moving lampreys</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>Lamprey</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Larva; Juvenile</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>10-12 mm; 91-118 mm; 80-122 mm</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>2% mortali</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>18; 34; 228; 263</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>Archimedean screw</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr"/>
+      <c r="P239" s="2" t="inlineStr"/>
+      <c r="Q239" s="2" t="inlineStr"/>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2013_Calles</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Calles</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/fwb.12199</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Success of a low-sloping rack for improving downstream passage of silver eels at a hydroelectric plant</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>European eel (A. anguilla); Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>20-18 mm</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>70% mortali; 60% mortali</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>40; 45; 2; 6; 20; 16</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>Siphon</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>Telemetry/tagging</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr"/>
+      <c r="Q240" s="2" t="inlineStr"/>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2001_Muir</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Muir</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>10.1577/1548-8675(2001)021&lt;0135:SOJSPT&gt;2.0.CO;2</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Survival of juvenile salmonids passing through bypass systems, turbines, and spillways with and without flow deflectors at Snake River dams</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Rainbow trout/steelhead (O. mykiss); Salmonids (general); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Smolt; Yearling/sub-adult</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>3.0% surviva; 81% surviva; 95.3% surviva; 86.5% surviva; 1% mortali; 73% surviva; 100% surviva; 4% mortali</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>Spillway</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>Telemetry/tagging; Mark-recapture/balloon-net</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr"/>
+      <c r="Q241" s="2" t="inlineStr"/>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2002_Backman</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Backman</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>10.1577/1548-8675(2002)022&lt;0579:GBTIIA&gt;2.0.CO;2</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Gas bubble trauma incidence in adult salmonids in the Columbia River Basin</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Gas supersaturation/GBT</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Rainbow trout/steelhead (O. mykiss); Sockeye/coho (Oncorhynchus); Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Adult</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr"/>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr"/>
+      <c r="O242" s="2" t="inlineStr"/>
+      <c r="P242" s="2" t="inlineStr"/>
+      <c r="Q242" s="2" t="inlineStr"/>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2003_McNabb</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>McNabb</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>10.1577/1548-8659(2003)132&lt;0326:POJCSA&gt;2.0.CO;2</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Passage of juvenile Chinook salmon and other fish species through Archimedes lifts and a Hidrostal pump at Red Bluff, California</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha)</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>34-42 mm; 58-74 mm; 32-42 mm; 28-39 mm; 17-218 mm; 31-41 mm</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>5% mortali; 29% mortali; 98.6% surviva; 94% surviva; 3% mortali</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>Pump; Archimedean screw</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr"/>
+      <c r="P243" s="2" t="inlineStr"/>
+      <c r="Q243" s="2" t="inlineStr"/>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>1985_Monten</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Monten</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Fish and turbines: fish injuries during passage through power station turbines</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr"/>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr"/>
+      <c r="O244" s="2" t="inlineStr"/>
+      <c r="P244" s="2" t="inlineStr"/>
+      <c r="Q244" s="2" t="inlineStr"/>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30 (merged from chapter archive)</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>1965_Foye</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Foye</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Effectsof pressure on survivalofsix species offish</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Barotrauma/pressure</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>Rainbow trout/steelhead (O. mykiss); Sockeye/coho (Oncorhynchus)</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Fry/fingerling; Smolt</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr"/>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr"/>
+      <c r="P245" s="2" t="inlineStr"/>
+      <c r="Q245" s="2" t="inlineStr"/>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>1968_Long</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Diel movement and distribution of juvenile anadromous fish in turbine intakes</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Rainbow trout/steelhead (O. mykiss); Sockeye/coho (Oncorhynchus); Lamprey; Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Fry/fingerling; Juvenile</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr"/>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>Kaplan</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr"/>
+      <c r="P246" s="2" t="inlineStr"/>
+      <c r="Q246" s="2" t="inlineStr"/>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>1969_Ebel</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Ebel</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr"/>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Supersaturationofnitrogeninthe Columbia River and itseffect on salmon</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Gas supersaturation/GBT</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Rainbow trout/steelhead (O. mykiss)</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Adult</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr"/>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>Spillway</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr"/>
+      <c r="P247" s="2" t="inlineStr"/>
+      <c r="Q247" s="2" t="inlineStr"/>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>1980_Bouck</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Bouck</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>10.1577/1548-8659(1980)109&lt;703:EOGBD&gt;2.0.CO;2</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Etiology of gas bubble disease</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Barotrauma/pressure; Cavitation; Gas supersaturation/GBT</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Larva</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>100% mortali</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr"/>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>Pressure/barotrauma chamber</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>Boyle's law</t>
+        </is>
+      </c>
+      <c r="Q248" s="2" t="inlineStr"/>
+      <c r="R248" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>1988_Davies</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Davies</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/j.1095-8649.1988.tb05565.x</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>A review of information relating to fish passage through turbines: Implications to tidal power schemes. Journa</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Cavitation; Turbulence</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>Smolts (unspec.); Atlantic salmon (Salmo salar); Sockeye/coho (Oncorhynchus); American shad (A. sapidissima)</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Adult</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>6% injury</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>Tidal</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr"/>
+      <c r="P249" s="2" t="inlineStr"/>
+      <c r="Q249" s="2" t="inlineStr"/>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>1995_Brookshier</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Brookshier</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>21st century Advanced Hydropower Turbine System</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr"/>
+      <c r="O250" s="2" t="inlineStr"/>
+      <c r="P250" s="2" t="inlineStr"/>
+      <c r="Q250" s="2" t="inlineStr"/>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>1997_Cada</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Cada</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Shaken, not stirred: the recipe for a fish-friendly turbine</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="2" t="inlineStr"/>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr"/>
+      <c r="M251" s="2" t="inlineStr"/>
+      <c r="N251" s="2" t="inlineStr"/>
+      <c r="O251" s="2" t="inlineStr"/>
+      <c r="P251" s="2" t="inlineStr"/>
+      <c r="Q251" s="2" t="inlineStr"/>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S251" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>1998_Haro</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Haro</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Behavior and Passage of Atlantic Salmon Smolts and Juvenile American Shad at Surface Bypasses</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Entrainment/impingement/screen</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>Atlantic salmon (Salmo salar); Sockeye/coho (Oncorhynchus); American shad (A. sapidissima); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Smolt</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>155-240 mm; 65-108 mm</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr"/>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>Weir</t>
+        </is>
+      </c>
+      <c r="O252" s="2" t="inlineStr"/>
+      <c r="P252" s="2" t="inlineStr"/>
+      <c r="Q252" s="2" t="inlineStr"/>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2000_Bickford</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Bickford</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Reanalysis and Interpretation of 25 years of Snake-Columbia River Juvenile Salmon Survival Studies. North Amer</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Rainbow trout/steelhead (O. mykiss); Sockeye/coho (Oncorhynchus); Salmonids (general); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Smolt</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>95% surviva</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>Kaplan; Spillway</t>
+        </is>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>Mark-recapture/balloon-net; Review/meta-analysis</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr"/>
+      <c r="Q253" s="2" t="inlineStr"/>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S253" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2001_Perry</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Buoyancy compensation of juvenile Chinook salmon implanted with two different size dummy transmitters. Transac</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Barotrauma/pressure</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>Chinook salmon (O. tshawytscha); Atlantic salmon (Salmo salar); Salmonids (general); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Juvenile; Smolt</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr"/>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr"/>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>Telemetry/tagging</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>Boyle's law; Neutral buoyancy / acclimation depth</t>
+        </is>
+      </c>
+      <c r="Q254" s="2" t="inlineStr"/>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2002_Skalski</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Skalski</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Effects of turbine operating efficiency on smolt passage survival</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>Salmonids (general); Smolts (unspec.)</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Smolt</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>82.0-342.9 mm</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>3.2% surviva; 61% surviva; 95% surviva; 96% surviva</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>Kaplan</t>
+        </is>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>Review/meta-analysis</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr"/>
+      <c r="Q255" s="2" t="inlineStr"/>
+      <c r="R255" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S255" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2007_Jansen</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Jansen</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Survival and movement of fish experimentally passed through a re-runnered turbine at the Kelsey Generating Station</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>American shad (A. sapidissima); Smolts (unspec.); Chinook salmon (O. tshawytscha); Salmonids (general)</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Yearling/sub-adult; Adult</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>156-450 mm; 451-769 mm; 105-646 mm; 452-769 mm; 326-562 mm; 296-433 mm</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>40% mortali; 88.9% surviva; 22% injury; 75.5% surviva; 20% injurie; 95% surviva; 90% surviva; 83.0% surviva; 43% injurie; 47% injury</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>60; 12; 24; 18; 6</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>Kaplan; Propeller/axial</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr"/>
+      <c r="P256" s="2" t="inlineStr"/>
+      <c r="Q256" s="2" t="inlineStr"/>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>Mined</t>
+        </is>
+      </c>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>ingested 2026-06-30</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
+          <t>title+abstract</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
